--- a/Plan to clear (terraform 003).xlsx
+++ b/Plan to clear (terraform 003).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xencia1-my.sharepoint.com/personal/prithivi_rajan_xencia_com/Documents/Documents/Prithivirajan_Notes/Devops/Terraform/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4616373-AA26-496F-9B75-522662007611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{D4616373-AA26-496F-9B75-522662007611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{420AB642-434D-4183-B30A-33FC94469B95}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{96BBD0D3-949E-4796-B6B3-BF25D435F142}"/>
+    <workbookView minimized="1" xWindow="1700" yWindow="4080" windowWidth="7500" windowHeight="6000" xr2:uid="{96BBD0D3-949E-4796-B6B3-BF25D435F142}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -911,7 +911,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -921,6 +921,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -952,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -964,6 +982,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1326,13 +1362,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1343,22 +1379,22 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1369,22 +1405,22 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -1395,9 +1431,9 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>19</v>
@@ -1628,4 +1664,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{75f2a99b-01fd-48f2-ac60-d4a7a44fd0cc}" enabled="0" method="" siteId="{75f2a99b-01fd-48f2-ac60-d4a7a44fd0cc}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/Plan to clear (terraform 003).xlsx
+++ b/Plan to clear (terraform 003).xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xencia1-my.sharepoint.com/personal/prithivi_rajan_xencia_com/Documents/Documents/Prithivirajan_Notes/Devops/Terraform/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{D4616373-AA26-496F-9B75-522662007611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{420AB642-434D-4183-B30A-33FC94469B95}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{D4616373-AA26-496F-9B75-522662007611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB90F1B-8996-4BC0-8B4C-C6CEDC1003F1}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1700" yWindow="4080" windowWidth="7500" windowHeight="6000" xr2:uid="{96BBD0D3-949E-4796-B6B3-BF25D435F142}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{96BBD0D3-949E-4796-B6B3-BF25D435F142}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Terraform 003" sheetId="1" r:id="rId1"/>
+    <sheet name="Azure Services" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="133">
   <si>
     <t>Month</t>
   </si>
@@ -883,14 +885,289 @@
       </rPr>
       <t xml:space="preserve"> for application performance monitoring. - Set up logging and metrics for cloud infrastructure.</t>
     </r>
+  </si>
+  <si>
+    <t>Azure SQL Database</t>
+  </si>
+  <si>
+    <t>Azure Cosmos DB</t>
+  </si>
+  <si>
+    <t>Azure Kubernetes Service (AKS)</t>
+  </si>
+  <si>
+    <t>Azure App Service</t>
+  </si>
+  <si>
+    <t>Azure Functions</t>
+  </si>
+  <si>
+    <t>Azure Virtual Network (VNet)</t>
+  </si>
+  <si>
+    <t>Azure Key Vault</t>
+  </si>
+  <si>
+    <t>Azure Load Balancer</t>
+  </si>
+  <si>
+    <t>Azure Service Bus</t>
+  </si>
+  <si>
+    <t>Azure Event Grid</t>
+  </si>
+  <si>
+    <t>Azure Event Hubs</t>
+  </si>
+  <si>
+    <t>Azure Logic Apps</t>
+  </si>
+  <si>
+    <t>Azure API Management</t>
+  </si>
+  <si>
+    <t>Azure Data Factory</t>
+  </si>
+  <si>
+    <t>Azure Synapse Analytics</t>
+  </si>
+  <si>
+    <t>Azure Application Insights</t>
+  </si>
+  <si>
+    <t>Azure Redis Cache</t>
+  </si>
+  <si>
+    <t>Azure Traffic Manager</t>
+  </si>
+  <si>
+    <t>Azure Front Door</t>
+  </si>
+  <si>
+    <t>Azure Container Instances</t>
+  </si>
+  <si>
+    <t>Azure DevOps</t>
+  </si>
+  <si>
+    <t>Azure Cognitive Services</t>
+  </si>
+  <si>
+    <t>IaaS (Infrastructure as a Service)</t>
+  </si>
+  <si>
+    <t>PaaS (Platform as a Service)</t>
+  </si>
+  <si>
+    <t>SaaS (Software as a Service)</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experience </t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Azure IaaS Service</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Compute</t>
+  </si>
+  <si>
+    <t>Azure Virtual Machines</t>
+  </si>
+  <si>
+    <t>Scalable Windows/Linux virtual machines</t>
+  </si>
+  <si>
+    <t>VM Scale Sets</t>
+  </si>
+  <si>
+    <t>Automatically scaled groups of VMs</t>
+  </si>
+  <si>
+    <t>Azure Dedicated Hosts</t>
+  </si>
+  <si>
+    <t>Physical servers for single-tenant VM hosting</t>
+  </si>
+  <si>
+    <t>Azure Spot VMs</t>
+  </si>
+  <si>
+    <t>Cost-effective VMs using unused capacity</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Azure Disks</t>
+  </si>
+  <si>
+    <t>Persistent block storage (HDD, SSD) for VMs</t>
+  </si>
+  <si>
+    <t>Azure Blob Storage (for IaaS)</t>
+  </si>
+  <si>
+    <t>Object storage often used with VMs</t>
+  </si>
+  <si>
+    <t>Azure Files</t>
+  </si>
+  <si>
+    <t>Fully managed file shares via SMB</t>
+  </si>
+  <si>
+    <t>Networking</t>
+  </si>
+  <si>
+    <t>Private network for resources</t>
+  </si>
+  <si>
+    <t>Layer 4 load balancing for inbound and outbound connections</t>
+  </si>
+  <si>
+    <t>Azure Application Gateway*</t>
+  </si>
+  <si>
+    <t>Layer 7 load balancing (often considered IaaS/PaaS hybrid)</t>
+  </si>
+  <si>
+    <t>Azure ExpressRoute</t>
+  </si>
+  <si>
+    <t>Private connection between Azure and on-premises infrastructure</t>
+  </si>
+  <si>
+    <t>Azure VPN Gateway</t>
+  </si>
+  <si>
+    <t>Encrypted tunnels for site-to-site or point-to-site connections</t>
+  </si>
+  <si>
+    <t>Network Security Groups (NSGs)</t>
+  </si>
+  <si>
+    <t>Control traffic to/from Azure resources</t>
+  </si>
+  <si>
+    <t>Azure Bastion</t>
+  </si>
+  <si>
+    <t>Secure RDP/SSH without exposing public IPs</t>
+  </si>
+  <si>
+    <t>Azure DDoS Protection</t>
+  </si>
+  <si>
+    <t>Protects VMs and networks from DDoS attacks</t>
+  </si>
+  <si>
+    <t>Identity &amp; Access</t>
+  </si>
+  <si>
+    <t>Manages access to VMs and network resources</t>
+  </si>
+  <si>
+    <t>Backup &amp; Recovery</t>
+  </si>
+  <si>
+    <t>Backs up VM data and configuration</t>
+  </si>
+  <si>
+    <t>Disaster recovery for VMs</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Monitors VM and infrastructure metrics</t>
+  </si>
+  <si>
+    <t>Log Analytics</t>
+  </si>
+  <si>
+    <t>Collects and queries logs from IaaS services</t>
+  </si>
+  <si>
+    <t>Azure Active Directory (access control for IaaS)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Azure Backup </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(also listed under SaaS)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Azure Site Recovery </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(also listed under SaaS)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Azure Monitor </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(core IaaS monitoring)</t>
+    </r>
+  </si>
+  <si>
+    <t>Azure Container Registry (ACR)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -910,8 +1187,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -939,6 +1224,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -970,35 +1267,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1345,320 +1662,698 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34BAFF85-A315-47D5-B5E5-8D63B3D53EBC}">
+  <dimension ref="B1:F21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D1" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B2" s="16"/>
+      <c r="C2" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B3" s="17"/>
+      <c r="C3" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B4" s="18"/>
+      <c r="C4" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D5" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="14"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D6" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="15"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="14"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D8" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D9" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D10" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="15"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D12" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="15"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D13" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D14" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="15"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D15" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="15"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D16" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="15"/>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D17" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="15"/>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D18" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="15"/>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D19" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" s="15"/>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D20" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D21" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D398D3F7-FA58-4F2A-B91A-F66E52280642}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="53.6328125" customWidth="1"/>
+    <col min="3" max="3" width="59" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="C10" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C12" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C14" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C16" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="C19" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
-        <v>56</v>
+      <c r="C21" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
